--- a/Food and Nutrition.xlsx
+++ b/Food and Nutrition.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Food APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB7C2F4-4109-46F9-B277-65DBF5B16CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E63578F-9E74-42EA-AD19-B3A93B39322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A853C7CF-0DCA-40B5-8163-06742DD74B7C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A853C7CF-0DCA-40B5-8163-06742DD74B7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B169" t="s">
         <v>297</v>
